--- a/data.mn/public/datasets/unemployment-rate-by-region.xlsx
+++ b/data.mn/public/datasets/unemployment-rate-by-region.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,19 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -425,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -734,6 +728,23 @@
         <v>7.3</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
